--- a/benchmarks/trajectories.xlsx
+++ b/benchmarks/trajectories.xlsx
@@ -137,10 +137,10 @@
     <t>child</t>
   </si>
   <si>
-    <t>bread-portion</t>
-  </si>
-  <si>
-    <t>content-portion</t>
+    <t>bread_portion</t>
+  </si>
+  <si>
+    <t>content_portion</t>
   </si>
   <si>
     <t>tray</t>
@@ -233,10 +233,10 @@
     <t>passenger</t>
   </si>
   <si>
-    <t>fast-elevator</t>
-  </si>
-  <si>
-    <t>slow-elevator</t>
+    <t>fast_elevator</t>
+  </si>
+  <si>
+    <t>slow_elevator</t>
   </si>
   <si>
     <t>0_elevators_traj</t>
@@ -785,7 +785,7 @@
     <t>vehicle</t>
   </si>
   <si>
-    <t>capacity-number</t>
+    <t>capacity_number</t>
   </si>
   <si>
     <t>0_transport_traj</t>
@@ -1240,7 +1240,7 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1249,7 +1249,7 @@
         <v>2</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>3</v>
@@ -1275,7 +1275,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1284,7 +1284,7 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>4</v>
@@ -1304,13 +1304,13 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -1319,7 +1319,7 @@
         <v>2</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4">
         <v>4</v>
@@ -1339,13 +1339,13 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1354,7 +1354,7 @@
         <v>2</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -1374,13 +1374,13 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1389,7 +1389,7 @@
         <v>2</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -1409,13 +1409,13 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1424,7 +1424,7 @@
         <v>2</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H7">
         <v>6</v>
@@ -1444,13 +1444,13 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C8">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1459,7 +1459,7 @@
         <v>2</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8">
         <v>6</v>
@@ -1485,7 +1485,7 @@
         <v>5</v>
       </c>
       <c r="D9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1494,7 +1494,7 @@
         <v>2</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H9">
         <v>7</v>
@@ -1514,13 +1514,13 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D10">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1529,7 +1529,7 @@
         <v>2</v>
       </c>
       <c r="G10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H10">
         <v>7</v>
@@ -1549,10 +1549,10 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D11">
         <v>35</v>
@@ -1622,19 +1622,19 @@
         <v>127</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1648,13 +1648,13 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1662,19 +1662,19 @@
         <v>129</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1682,19 +1682,19 @@
         <v>130</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1702,19 +1702,19 @@
         <v>131</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1722,19 +1722,19 @@
         <v>132</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1742,19 +1742,19 @@
         <v>133</v>
       </c>
       <c r="B8">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C8">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8">
         <v>2</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1762,19 +1762,19 @@
         <v>134</v>
       </c>
       <c r="B9">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C9">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9">
         <v>2</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1782,19 +1782,19 @@
         <v>135</v>
       </c>
       <c r="B10">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C10">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10">
         <v>2</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1802,19 +1802,19 @@
         <v>136</v>
       </c>
       <c r="B11">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C11">
+        <v>28</v>
+      </c>
+      <c r="D11">
         <v>14</v>
       </c>
-      <c r="D11">
-        <v>13</v>
-      </c>
       <c r="E11">
         <v>2</v>
       </c>
       <c r="F11">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1900,10 +1900,10 @@
         <v>140</v>
       </c>
       <c r="B4">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -1920,10 +1920,10 @@
         <v>141</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>8</v>
@@ -1940,10 +1940,10 @@
         <v>142</v>
       </c>
       <c r="B6">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D6">
         <v>12</v>
@@ -1960,10 +1960,10 @@
         <v>143</v>
       </c>
       <c r="B7">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -2000,10 +2000,10 @@
         <v>145</v>
       </c>
       <c r="B9">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>12</v>
@@ -2020,10 +2020,10 @@
         <v>146</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D10">
         <v>16</v>
@@ -2040,10 +2040,10 @@
         <v>147</v>
       </c>
       <c r="B11">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C11">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D11">
         <v>14</v>
@@ -2184,13 +2184,13 @@
         <v>153</v>
       </c>
       <c r="B5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -2202,7 +2202,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2210,13 +2210,13 @@
         <v>154</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -2228,7 +2228,7 @@
         <v>2</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2236,13 +2236,13 @@
         <v>155</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -2254,7 +2254,7 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2262,13 +2262,13 @@
         <v>156</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -2280,7 +2280,7 @@
         <v>3</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2288,10 +2288,10 @@
         <v>157</v>
       </c>
       <c r="B9">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C9">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D9">
         <v>20</v>
@@ -2320,7 +2320,7 @@
         <v>5</v>
       </c>
       <c r="D10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10">
         <v>6</v>
@@ -2332,7 +2332,7 @@
         <v>4</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2340,13 +2340,13 @@
         <v>159</v>
       </c>
       <c r="B11">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C11">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11">
         <v>6</v>
@@ -2358,7 +2358,7 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2404,10 +2404,10 @@
         <v>161</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>7</v>
@@ -2424,10 +2424,10 @@
         <v>162</v>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D3">
         <v>7</v>
@@ -2444,10 +2444,10 @@
         <v>163</v>
       </c>
       <c r="B4">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D4">
         <v>17</v>
@@ -2464,10 +2464,10 @@
         <v>164</v>
       </c>
       <c r="B5">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C5">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>17</v>
@@ -2484,10 +2484,10 @@
         <v>165</v>
       </c>
       <c r="B6">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D6">
         <v>31</v>
@@ -2504,10 +2504,10 @@
         <v>166</v>
       </c>
       <c r="B7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>31</v>
@@ -2524,10 +2524,10 @@
         <v>167</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D8">
         <v>49</v>
@@ -2544,10 +2544,10 @@
         <v>168</v>
       </c>
       <c r="B9">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>49</v>
@@ -2564,10 +2564,10 @@
         <v>169</v>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C10">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D10">
         <v>71</v>
@@ -2682,10 +2682,10 @@
         <v>174</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>8</v>
@@ -2722,10 +2722,10 @@
         <v>176</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D6">
         <v>11</v>
@@ -2742,10 +2742,10 @@
         <v>177</v>
       </c>
       <c r="B7">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D7">
         <v>13</v>
@@ -2934,10 +2934,10 @@
         <v>190</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <v>14</v>
@@ -2969,10 +2969,10 @@
         <v>191</v>
       </c>
       <c r="B4">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <v>18</v>
@@ -3004,13 +3004,13 @@
         <v>192</v>
       </c>
       <c r="B5">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C5">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -3028,7 +3028,7 @@
         <v>6</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <v>3</v>
@@ -3039,13 +3039,13 @@
         <v>193</v>
       </c>
       <c r="B6">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -3063,7 +3063,7 @@
         <v>7</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>3</v>
@@ -3074,13 +3074,13 @@
         <v>194</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -3098,7 +3098,7 @@
         <v>8</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>4</v>
@@ -3109,13 +3109,13 @@
         <v>195</v>
       </c>
       <c r="B8">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -3133,7 +3133,7 @@
         <v>9</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K8">
         <v>4</v>
@@ -3144,13 +3144,13 @@
         <v>196</v>
       </c>
       <c r="B9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -3168,7 +3168,7 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K9">
         <v>5</v>
@@ -3179,10 +3179,10 @@
         <v>197</v>
       </c>
       <c r="B10">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>36</v>
@@ -3214,10 +3214,10 @@
         <v>198</v>
       </c>
       <c r="B11">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>39</v>
@@ -3295,10 +3295,10 @@
         <v>202</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>9</v>
@@ -3321,10 +3321,10 @@
         <v>203</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D3">
         <v>14</v>
@@ -3347,19 +3347,19 @@
         <v>204</v>
       </c>
       <c r="B4">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -3373,19 +3373,19 @@
         <v>205</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -3399,19 +3399,19 @@
         <v>206</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E6">
         <v>5</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -3425,19 +3425,19 @@
         <v>207</v>
       </c>
       <c r="B7">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E7">
         <v>5</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -3451,19 +3451,19 @@
         <v>208</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C8">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D8">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E8">
         <v>6</v>
       </c>
       <c r="F8">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G8">
         <v>4</v>
@@ -3477,19 +3477,19 @@
         <v>209</v>
       </c>
       <c r="B9">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E9">
         <v>6</v>
       </c>
       <c r="F9">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -3503,19 +3503,19 @@
         <v>210</v>
       </c>
       <c r="B10">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C10">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D10">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E10">
         <v>7</v>
       </c>
       <c r="F10">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -3529,19 +3529,19 @@
         <v>211</v>
       </c>
       <c r="B11">
+        <v>23</v>
+      </c>
+      <c r="C11">
         <v>24</v>
       </c>
-      <c r="C11">
-        <v>25</v>
-      </c>
       <c r="D11">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E11">
         <v>7</v>
       </c>
       <c r="F11">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>6</v>
@@ -3641,10 +3641,10 @@
         <v>216</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D4">
         <v>41</v>
@@ -3664,10 +3664,10 @@
         <v>217</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>41</v>
@@ -3687,10 +3687,10 @@
         <v>218</v>
       </c>
       <c r="B6">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D6">
         <v>55</v>
@@ -3710,10 +3710,10 @@
         <v>219</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D7">
         <v>55</v>
@@ -3733,10 +3733,10 @@
         <v>220</v>
       </c>
       <c r="B8">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C8">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D8">
         <v>71</v>
@@ -3756,10 +3756,10 @@
         <v>221</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>71</v>
@@ -3779,10 +3779,10 @@
         <v>222</v>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C10">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D10">
         <v>107</v>
@@ -3802,10 +3802,10 @@
         <v>223</v>
       </c>
       <c r="B11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11">
         <v>107</v>
@@ -3923,10 +3923,10 @@
         <v>229</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D4">
         <v>14</v>
@@ -3949,10 +3949,10 @@
         <v>230</v>
       </c>
       <c r="B5">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>17</v>
@@ -3975,10 +3975,10 @@
         <v>231</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>20</v>
@@ -4001,10 +4001,10 @@
         <v>232</v>
       </c>
       <c r="B7">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C7">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7">
         <v>23</v>
@@ -4027,10 +4027,10 @@
         <v>233</v>
       </c>
       <c r="B8">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>26</v>
@@ -4053,10 +4053,10 @@
         <v>234</v>
       </c>
       <c r="B9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9">
         <v>29</v>
@@ -4208,10 +4208,10 @@
         <v>240</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D3">
         <v>11</v>
@@ -4237,10 +4237,10 @@
         <v>241</v>
       </c>
       <c r="B4">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D4">
         <v>12</v>
@@ -4266,10 +4266,10 @@
         <v>242</v>
       </c>
       <c r="B5">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>13</v>
@@ -4295,10 +4295,10 @@
         <v>243</v>
       </c>
       <c r="B6">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D6">
         <v>16</v>
@@ -4324,10 +4324,10 @@
         <v>244</v>
       </c>
       <c r="B7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>19</v>
@@ -4353,10 +4353,10 @@
         <v>245</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D8">
         <v>20</v>
@@ -4382,10 +4382,10 @@
         <v>246</v>
       </c>
       <c r="B9">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>23</v>
@@ -4411,10 +4411,10 @@
         <v>247</v>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C10">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D10">
         <v>24</v>
@@ -4537,10 +4537,10 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -4588,10 +4588,10 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -4605,10 +4605,10 @@
         <v>28</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D8">
         <v>6</v>
@@ -4622,10 +4622,10 @@
         <v>29</v>
       </c>
       <c r="B9">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>6</v>
@@ -4639,10 +4639,10 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C10">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D10">
         <v>7</v>
@@ -4656,10 +4656,10 @@
         <v>31</v>
       </c>
       <c r="B11">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C11">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D11">
         <v>7</v>
@@ -4750,16 +4750,16 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -4770,22 +4770,22 @@
         <v>253</v>
       </c>
       <c r="B4">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -4796,22 +4796,22 @@
         <v>254</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -4822,10 +4822,10 @@
         <v>255</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D6">
         <v>27</v>
@@ -4848,22 +4848,22 @@
         <v>256</v>
       </c>
       <c r="B7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H7">
         <v>5</v>
@@ -4874,22 +4874,22 @@
         <v>257</v>
       </c>
       <c r="B8">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D8">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H8">
         <v>5</v>
@@ -4900,22 +4900,22 @@
         <v>258</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C9">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D9">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H9">
         <v>5</v>
@@ -4926,10 +4926,10 @@
         <v>259</v>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C10">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D10">
         <v>44</v>
@@ -4952,10 +4952,10 @@
         <v>260</v>
       </c>
       <c r="B11">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D11">
         <v>53</v>
@@ -5095,10 +5095,10 @@
         <v>40</v>
       </c>
       <c r="B4">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <v>24</v>
@@ -5127,10 +5127,10 @@
         <v>41</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D5">
         <v>24</v>
@@ -5159,10 +5159,10 @@
         <v>42</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>29</v>
@@ -5191,10 +5191,10 @@
         <v>43</v>
       </c>
       <c r="B7">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>28</v>
@@ -5223,10 +5223,10 @@
         <v>44</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D8">
         <v>33</v>
@@ -5255,10 +5255,10 @@
         <v>45</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C9">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D9">
         <v>32</v>
@@ -5287,10 +5287,10 @@
         <v>46</v>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>39</v>
@@ -5319,10 +5319,10 @@
         <v>47</v>
       </c>
       <c r="B11">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>38</v>
@@ -5468,10 +5468,10 @@
         <v>56</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D4">
         <v>19</v>
@@ -5500,10 +5500,10 @@
         <v>57</v>
       </c>
       <c r="B5">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D5">
         <v>24</v>
@@ -5532,10 +5532,10 @@
         <v>58</v>
       </c>
       <c r="B6">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D6">
         <v>27</v>
@@ -5564,10 +5564,10 @@
         <v>59</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>30</v>
@@ -5596,10 +5596,10 @@
         <v>60</v>
       </c>
       <c r="B8">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C8">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D8">
         <v>32</v>
@@ -5628,10 +5628,10 @@
         <v>61</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D9">
         <v>35</v>
@@ -5660,10 +5660,10 @@
         <v>62</v>
       </c>
       <c r="B10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D10">
         <v>38</v>
@@ -5692,10 +5692,10 @@
         <v>63</v>
       </c>
       <c r="B11">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D11">
         <v>43</v>
@@ -5769,25 +5769,25 @@
         <v>68</v>
       </c>
       <c r="B2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -5801,10 +5801,10 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -5813,7 +5813,7 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -5821,19 +5821,19 @@
         <v>70</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -5847,10 +5847,10 @@
         <v>71</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D5">
         <v>14</v>
@@ -5873,19 +5873,19 @@
         <v>72</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>6</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -5899,10 +5899,10 @@
         <v>73</v>
       </c>
       <c r="B7">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C7">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D7">
         <v>13</v>
@@ -5925,19 +5925,19 @@
         <v>74</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8">
         <v>7</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -5951,10 +5951,10 @@
         <v>75</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C9">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D9">
         <v>17</v>
@@ -5977,19 +5977,19 @@
         <v>76</v>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C10">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10">
         <v>8</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -6003,10 +6003,10 @@
         <v>77</v>
       </c>
       <c r="B11">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D11">
         <v>18</v>
@@ -6127,10 +6127,10 @@
         <v>83</v>
       </c>
       <c r="B5">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C5">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D5">
         <v>10</v>
@@ -6147,10 +6147,10 @@
         <v>84</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D6">
         <v>16</v>
@@ -6167,10 +6167,10 @@
         <v>85</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>14</v>
@@ -6187,10 +6187,10 @@
         <v>86</v>
       </c>
       <c r="B8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8">
         <v>20</v>
@@ -6207,10 +6207,10 @@
         <v>87</v>
       </c>
       <c r="B9">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C9">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D9">
         <v>18</v>
@@ -6227,10 +6227,10 @@
         <v>88</v>
       </c>
       <c r="B10">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C10">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D10">
         <v>24</v>
@@ -6247,10 +6247,10 @@
         <v>89</v>
       </c>
       <c r="B11">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="C11">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D11">
         <v>22</v>
@@ -6377,10 +6377,10 @@
         <v>96</v>
       </c>
       <c r="B5">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D5">
         <v>46</v>
@@ -6446,10 +6446,10 @@
         <v>99</v>
       </c>
       <c r="B8">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C8">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D8">
         <v>61</v>
@@ -6469,10 +6469,10 @@
         <v>100</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>69</v>
@@ -6492,10 +6492,10 @@
         <v>101</v>
       </c>
       <c r="B10">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C10">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D10">
         <v>68</v>
@@ -6515,10 +6515,10 @@
         <v>102</v>
       </c>
       <c r="B11">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C11">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D11">
         <v>78</v>
@@ -6606,10 +6606,10 @@
         <v>106</v>
       </c>
       <c r="B4">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>12</v>
@@ -6623,10 +6623,10 @@
         <v>107</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D5">
         <v>16</v>
@@ -6640,10 +6640,10 @@
         <v>108</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>20</v>
@@ -6657,10 +6657,10 @@
         <v>109</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D7">
         <v>20</v>
@@ -6674,10 +6674,10 @@
         <v>110</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C8">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D8">
         <v>25</v>
@@ -6691,10 +6691,10 @@
         <v>111</v>
       </c>
       <c r="B9">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C9">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D9">
         <v>30</v>
@@ -6708,10 +6708,10 @@
         <v>112</v>
       </c>
       <c r="B10">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>30</v>
@@ -6725,10 +6725,10 @@
         <v>113</v>
       </c>
       <c r="B11">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C11">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D11">
         <v>36</v>
@@ -6813,10 +6813,10 @@
         <v>118</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3">
         <v>9</v>
@@ -6839,10 +6839,10 @@
         <v>119</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -6865,10 +6865,10 @@
         <v>120</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D5">
         <v>15</v>
@@ -6891,10 +6891,10 @@
         <v>121</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6">
         <v>16</v>
@@ -6917,10 +6917,10 @@
         <v>122</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D7">
         <v>18</v>
@@ -6943,10 +6943,10 @@
         <v>123</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C8">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D8">
         <v>22</v>
@@ -6995,10 +6995,10 @@
         <v>125</v>
       </c>
       <c r="B10">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C10">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D10">
         <v>25</v>
@@ -7021,10 +7021,10 @@
         <v>126</v>
       </c>
       <c r="B11">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C11">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D11">
         <v>30</v>
